--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/lib-gral-bdo-o-higgins.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3233.75</v>
+        <v>3216.04</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2381.65</v>
+        <v>2439.56</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2885.4</v>
+        <v>2873.23</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1373.58</v>
+        <v>1382.62</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3024.08</v>
+        <v>3007.61</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>564.6799999999999</v>
+        <v>561.25</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>14120.64</v>
+        <v>14155.38</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8506.23</v>
+        <v>8513.559999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10863.88</v>
+        <v>10801.48</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1174.38</v>
+        <v>1147.05</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3621.86</v>
+        <v>3632.41</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>13985.76</v>
+        <v>14144.81</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6348.09</v>
+        <v>6320.27</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7736.05</v>
+        <v>7605.35</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>577.41</v>
+        <v>573.83</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2656.83</v>
+        <v>2662.92</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1639.31</v>
+        <v>1643.07</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2914.38</v>
+        <v>2933.89</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6106.33</v>
+        <v>6149.06</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>404.21</v>
+        <v>407.04</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3730.99</v>
+        <v>3757.1</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8338.1</v>
+        <v>8396.450000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2773.77</v>
+        <v>2765.01</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7363.1</v>
+        <v>7339.85</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8112.58</v>
+        <v>8094.93</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4722.57</v>
+        <v>4713.11</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3067.77</v>
+        <v>3052.68</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/lib-gral-bdo-o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3634-525-CM25</t>
+          <t>4562-174-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA SIBESA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.126.547-4</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3216.04</v>
+        <v>1100.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2817-12-CM26</t>
+          <t>4562-183-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2439.56</v>
+        <v>5192.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2675-35-CM26</t>
+          <t>3634-525-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>CONSTRUCTORA SIBESA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.126.547-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2873.23</v>
+        <v>3216.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4562-44-CM26</t>
+          <t>2817-12-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1382.62</v>
+        <v>2439.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1398-202-CM26</t>
+          <t>2675-35-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3007.61</v>
+        <v>2873.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4562-72-CM26</t>
+          <t>4562-44-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>561.25</v>
+        <v>1382.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2402-40-CM26</t>
+          <t>1398-202-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>14155.38</v>
+        <v>3007.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2401-264-CM26</t>
+          <t>4562-72-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8513.559999999999</v>
+        <v>561.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4562-157-CM26</t>
+          <t>2402-40-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10801.48</v>
+        <v>14155.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2080-2942-CM26</t>
+          <t>2401-264-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1147.05</v>
+        <v>8513.559999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2675-118-CM26</t>
+          <t>4562-157-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3632.41</v>
+        <v>10801.48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1079563-151-CM26</t>
+          <t>2080-2942-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>14144.81</v>
+        <v>1147.05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4562-244-CM26</t>
+          <t>2675-118-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6320.27</v>
+        <v>3632.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2401-545-CM26</t>
+          <t>1079563-151-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>SECCIÓN COMPRAS VI ZONA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7605.35</v>
+        <v>14144.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2817-299-CM26</t>
+          <t>4562-244-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>573.83</v>
+        <v>6320.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3634-288-CM26</t>
+          <t>2401-545-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2662.92</v>
+        <v>7605.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4371-267-CM26</t>
+          <t>2817-299-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1643.07</v>
+        <v>573.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2675-293-CM26</t>
+          <t>3634-288-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2933.89</v>
+        <v>2662.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4371-273-CM26</t>
+          <t>4371-267-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6149.06</v>
+        <v>1643.07</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3181-310-CM26</t>
+          <t>2675-293-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>407.04</v>
+        <v>2933.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2401-698-CM26</t>
+          <t>4371-273-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3757.1</v>
+        <v>6149.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2401-699-CM26</t>
+          <t>3181-310-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8396.450000000001</v>
+        <v>407.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2401-703-CM26</t>
+          <t>2401-698-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2765.01</v>
+        <v>3757.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2401-704-CM26</t>
+          <t>2401-699-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7339.85</v>
+        <v>8396.450000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2401-708-CM26</t>
+          <t>2401-703-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8094.93</v>
+        <v>2765.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2568-137-CM26</t>
+          <t>2401-704-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4713.11</v>
+        <v>7339.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2675-322-CM26</t>
+          <t>2401-708-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,6 +2155,128 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
+        <v>8094.93</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2568-137-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>4713.11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2675-322-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.080.500-6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
         <v>3052.68</v>
       </c>
     </row>
